--- a/outputs/Rice_(high_quality)_percentile_classification_matrix.xlsx
+++ b/outputs/Rice_(high_quality)_percentile_classification_matrix.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2550" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2550" uniqueCount="110">
   <si>
     <t>2020 May</t>
   </si>
@@ -343,76 +343,7 @@
     <t>Minimal</t>
   </si>
   <si>
-    <t>Alert</t>
-  </si>
-  <si>
-    <t>Alarm</t>
-  </si>
-  <si>
-    <t>17%</t>
-  </si>
-  <si>
-    <t>20%</t>
-  </si>
-  <si>
-    <t>21%</t>
-  </si>
-  <si>
-    <t>27%</t>
-  </si>
-  <si>
-    <t>24%</t>
-  </si>
-  <si>
-    <t>1%</t>
-  </si>
-  <si>
-    <t>30%</t>
-  </si>
-  <si>
-    <t>14%</t>
-  </si>
-  <si>
-    <t>28%</t>
-  </si>
-  <si>
-    <t>6%</t>
-  </si>
-  <si>
-    <t>25%</t>
-  </si>
-  <si>
-    <t>10%</t>
-  </si>
-  <si>
-    <t>32%</t>
-  </si>
-  <si>
-    <t>8%</t>
-  </si>
-  <si>
-    <t>23%</t>
-  </si>
-  <si>
-    <t>11%</t>
-  </si>
-  <si>
-    <t>7%</t>
-  </si>
-  <si>
-    <t>4%</t>
-  </si>
-  <si>
-    <t>13%</t>
-  </si>
-  <si>
     <t>0%</t>
-  </si>
-  <si>
-    <t>31%</t>
-  </si>
-  <si>
-    <t>34%</t>
   </si>
 </sst>
 </file>
@@ -1090,31 +1021,31 @@
         <v>108</v>
       </c>
       <c r="W2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="X2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="Y2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="Z2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AA2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AB2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AC2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AD2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AE2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AF2" t="s">
         <v>108</v>
@@ -1132,31 +1063,31 @@
         <v>108</v>
       </c>
       <c r="AK2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AL2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AM2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AN2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AO2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AP2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AQ2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AR2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AS2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AT2" t="s">
         <v>108</v>
@@ -1231,22 +1162,22 @@
         <v>108</v>
       </c>
       <c r="BR2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BS2" t="s">
         <v>108</v>
       </c>
       <c r="BT2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BU2" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="BV2" t="s">
-        <v>126</v>
+        <v>109</v>
       </c>
       <c r="BW2" t="s">
-        <v>119</v>
+        <v>109</v>
       </c>
     </row>
     <row r="3" spans="1:75">
@@ -1326,46 +1257,46 @@
         <v>108</v>
       </c>
       <c r="Z3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AA3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AB3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AC3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AD3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AE3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AF3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AG3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AH3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AI3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AJ3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AK3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AL3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AM3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AN3" t="s">
         <v>108</v>
@@ -1452,28 +1383,28 @@
         <v>108</v>
       </c>
       <c r="BP3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BQ3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BR3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BS3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BT3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BU3" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="BV3" t="s">
-        <v>127</v>
+        <v>109</v>
       </c>
       <c r="BW3" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
     </row>
     <row r="4" spans="1:75">
@@ -1550,61 +1481,61 @@
         <v>108</v>
       </c>
       <c r="Y4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="Z4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AA4" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AB4" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AC4" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AD4" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AE4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AF4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AG4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AH4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AI4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AJ4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AK4" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AL4" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AM4" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AN4" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AO4" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AP4" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AQ4" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AR4" t="s">
         <v>108</v>
@@ -1682,25 +1613,25 @@
         <v>108</v>
       </c>
       <c r="BQ4" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BR4" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BS4" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BT4" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BU4" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="BV4" t="s">
-        <v>126</v>
+        <v>109</v>
       </c>
       <c r="BW4" t="s">
-        <v>123</v>
+        <v>109</v>
       </c>
     </row>
     <row r="5" spans="1:75">
@@ -1780,55 +1711,55 @@
         <v>108</v>
       </c>
       <c r="Z5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AA5" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AB5" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AC5" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AD5" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AE5" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AF5" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AG5" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AH5" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AI5" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AJ5" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AK5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AL5" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AM5" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AN5" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AO5" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AP5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AQ5" t="s">
         <v>108</v>
@@ -1906,28 +1837,28 @@
         <v>108</v>
       </c>
       <c r="BP5" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BQ5" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BR5" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BS5" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BT5" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BU5" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="BV5" t="s">
-        <v>128</v>
+        <v>109</v>
       </c>
       <c r="BW5" t="s">
-        <v>131</v>
+        <v>109</v>
       </c>
     </row>
     <row r="6" spans="1:75">
@@ -2010,58 +1941,58 @@
         <v>108</v>
       </c>
       <c r="AA6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AB6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AC6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AD6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AE6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AF6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AG6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AH6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AI6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AJ6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AK6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AL6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AM6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AN6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AO6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AP6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AQ6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AR6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AS6" t="s">
         <v>108</v>
@@ -2139,22 +2070,22 @@
         <v>108</v>
       </c>
       <c r="BR6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BS6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BT6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BU6" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="BV6" t="s">
-        <v>120</v>
+        <v>109</v>
       </c>
       <c r="BW6" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
     </row>
     <row r="7" spans="1:75">
@@ -2270,7 +2201,7 @@
         <v>108</v>
       </c>
       <c r="AL7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AM7" t="s">
         <v>108</v>
@@ -2285,7 +2216,7 @@
         <v>108</v>
       </c>
       <c r="AQ7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AR7" t="s">
         <v>108</v>
@@ -2306,7 +2237,7 @@
         <v>108</v>
       </c>
       <c r="AX7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AY7" t="s">
         <v>108</v>
@@ -2372,16 +2303,16 @@
         <v>108</v>
       </c>
       <c r="BT7" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BU7" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="BV7" t="s">
-        <v>128</v>
+        <v>109</v>
       </c>
       <c r="BW7" t="s">
-        <v>120</v>
+        <v>109</v>
       </c>
     </row>
     <row r="8" spans="1:75">
@@ -2461,52 +2392,52 @@
         <v>108</v>
       </c>
       <c r="Z8" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AA8" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AB8" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AC8" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AD8" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AE8" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AF8" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AG8" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AH8" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AI8" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AJ8" t="s">
         <v>108</v>
       </c>
       <c r="AK8" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AL8" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AM8" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AN8" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AO8" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AP8" t="s">
         <v>108</v>
@@ -2581,34 +2512,34 @@
         <v>108</v>
       </c>
       <c r="BN8" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BO8" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BP8" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BQ8" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BR8" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BS8" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BT8" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BU8" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="BV8" t="s">
-        <v>127</v>
+        <v>109</v>
       </c>
       <c r="BW8" t="s">
-        <v>131</v>
+        <v>109</v>
       </c>
     </row>
     <row r="9" spans="1:75">
@@ -2688,55 +2619,55 @@
         <v>108</v>
       </c>
       <c r="Z9" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AA9" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AB9" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AC9" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AD9" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AE9" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AF9" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AG9" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AH9" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AI9" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AJ9" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AK9" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AL9" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AM9" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AN9" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AO9" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AP9" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AQ9" t="s">
         <v>108</v>
@@ -2817,25 +2748,25 @@
         <v>108</v>
       </c>
       <c r="BQ9" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BR9" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BS9" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BT9" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BU9" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="BV9" t="s">
-        <v>129</v>
+        <v>109</v>
       </c>
       <c r="BW9" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
     </row>
     <row r="10" spans="1:75">
@@ -2918,55 +2849,55 @@
         <v>108</v>
       </c>
       <c r="AA10" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AB10" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AC10" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AD10" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AE10" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AF10" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AG10" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AH10" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AI10" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AJ10" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AK10" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AL10" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AM10" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AN10" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AO10" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AP10" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AQ10" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AR10" t="s">
         <v>108</v>
@@ -3041,28 +2972,28 @@
         <v>108</v>
       </c>
       <c r="BP10" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BQ10" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BR10" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BS10" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BT10" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BU10" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="BV10" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="BW10" t="s">
-        <v>131</v>
+        <v>109</v>
       </c>
     </row>
     <row r="11" spans="1:75">
@@ -3151,37 +3082,37 @@
         <v>108</v>
       </c>
       <c r="AC11" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AD11" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AE11" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AF11" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AG11" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AH11" t="s">
         <v>108</v>
       </c>
       <c r="AI11" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AJ11" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AK11" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AL11" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AM11" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AN11" t="s">
         <v>108</v>
@@ -3262,34 +3193,34 @@
         <v>108</v>
       </c>
       <c r="BN11" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BO11" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BP11" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BQ11" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BR11" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BS11" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BT11" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BU11" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="BV11" t="s">
-        <v>122</v>
+        <v>109</v>
       </c>
       <c r="BW11" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
     </row>
     <row r="12" spans="1:75">
@@ -3369,58 +3300,58 @@
         <v>108</v>
       </c>
       <c r="Z12" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AA12" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AB12" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AC12" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AD12" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AE12" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AF12" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AG12" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AH12" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AI12" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AJ12" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AK12" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AL12" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AM12" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AN12" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AO12" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AP12" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AQ12" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AR12" t="s">
         <v>108</v>
@@ -3498,10 +3429,10 @@
         <v>108</v>
       </c>
       <c r="BQ12" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BR12" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BS12" t="s">
         <v>108</v>
@@ -3510,13 +3441,13 @@
         <v>108</v>
       </c>
       <c r="BU12" t="s">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="BV12" t="s">
-        <v>130</v>
+        <v>109</v>
       </c>
       <c r="BW12" t="s">
-        <v>119</v>
+        <v>109</v>
       </c>
     </row>
     <row r="13" spans="1:75">
@@ -3596,58 +3527,58 @@
         <v>108</v>
       </c>
       <c r="Z13" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AA13" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AB13" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AC13" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AD13" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AE13" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AF13" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AG13" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AH13" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AI13" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AJ13" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AK13" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AL13" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AM13" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AN13" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AO13" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AP13" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AQ13" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AR13" t="s">
         <v>108</v>
@@ -3710,7 +3641,7 @@
         <v>108</v>
       </c>
       <c r="BL13" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BM13" t="s">
         <v>108</v>
@@ -3722,28 +3653,28 @@
         <v>108</v>
       </c>
       <c r="BP13" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BQ13" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BR13" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BS13" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BT13" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BU13" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="BV13" t="s">
-        <v>127</v>
+        <v>109</v>
       </c>
       <c r="BW13" t="s">
-        <v>132</v>
+        <v>109</v>
       </c>
     </row>
     <row r="14" spans="1:75">
@@ -3826,22 +3757,22 @@
         <v>108</v>
       </c>
       <c r="AA14" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AB14" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AC14" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AD14" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AE14" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AF14" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AG14" t="s">
         <v>108</v>
@@ -3850,16 +3781,16 @@
         <v>108</v>
       </c>
       <c r="AI14" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AJ14" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AK14" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AL14" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AM14" t="s">
         <v>108</v>
@@ -3871,7 +3802,7 @@
         <v>108</v>
       </c>
       <c r="AP14" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AQ14" t="s">
         <v>108</v>
@@ -3949,28 +3880,28 @@
         <v>108</v>
       </c>
       <c r="BP14" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BQ14" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BR14" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BS14" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BT14" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BU14" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="BV14" t="s">
-        <v>124</v>
+        <v>109</v>
       </c>
       <c r="BW14" t="s">
-        <v>125</v>
+        <v>109</v>
       </c>
     </row>
     <row r="15" spans="1:75">
@@ -4053,46 +3984,46 @@
         <v>108</v>
       </c>
       <c r="AA15" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AB15" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AC15" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AD15" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AE15" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AF15" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AG15" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AH15" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AI15" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AJ15" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AK15" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AL15" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AM15" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AN15" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AO15" t="s">
         <v>108</v>
@@ -4110,7 +4041,7 @@
         <v>108</v>
       </c>
       <c r="AT15" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AU15" t="s">
         <v>108</v>
@@ -4119,7 +4050,7 @@
         <v>108</v>
       </c>
       <c r="AW15" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AX15" t="s">
         <v>108</v>
@@ -4179,25 +4110,25 @@
         <v>108</v>
       </c>
       <c r="BQ15" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BR15" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BS15" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BT15" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BU15" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="BV15" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="BW15" t="s">
-        <v>119</v>
+        <v>109</v>
       </c>
     </row>
     <row r="16" spans="1:75">
@@ -4277,58 +4208,58 @@
         <v>108</v>
       </c>
       <c r="Z16" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AA16" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AB16" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AC16" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AD16" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AE16" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AF16" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AG16" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AH16" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AI16" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AJ16" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AK16" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AL16" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AM16" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AN16" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AO16" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AP16" t="s">
         <v>108</v>
       </c>
       <c r="AQ16" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AR16" t="s">
         <v>108</v>
@@ -4388,10 +4319,10 @@
         <v>108</v>
       </c>
       <c r="BK16" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BL16" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BM16" t="s">
         <v>108</v>
@@ -4403,28 +4334,28 @@
         <v>108</v>
       </c>
       <c r="BP16" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BQ16" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BR16" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BS16" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BT16" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BU16" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="BV16" t="s">
-        <v>122</v>
+        <v>109</v>
       </c>
       <c r="BW16" t="s">
-        <v>132</v>
+        <v>109</v>
       </c>
     </row>
     <row r="17" spans="1:75">
@@ -4501,58 +4432,58 @@
         <v>108</v>
       </c>
       <c r="Y17" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="Z17" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AA17" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AB17" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AC17" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AD17" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AE17" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AF17" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AG17" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AH17" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AI17" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AJ17" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AK17" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AL17" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AM17" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AN17" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AO17" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AP17" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AQ17" t="s">
         <v>108</v>
@@ -4630,28 +4561,28 @@
         <v>108</v>
       </c>
       <c r="BP17" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BQ17" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BR17" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BS17" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BT17" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BU17" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="BV17" t="s">
-        <v>129</v>
+        <v>109</v>
       </c>
       <c r="BW17" t="s">
-        <v>123</v>
+        <v>109</v>
       </c>
     </row>
     <row r="18" spans="1:75">
@@ -4731,55 +4662,55 @@
         <v>108</v>
       </c>
       <c r="Z18" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AA18" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AB18" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AC18" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AD18" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AE18" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AF18" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AG18" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AH18" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AI18" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AJ18" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AK18" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AL18" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AM18" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AN18" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AO18" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AP18" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AQ18" t="s">
         <v>108</v>
@@ -4857,28 +4788,28 @@
         <v>108</v>
       </c>
       <c r="BP18" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BQ18" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BR18" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BS18" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BT18" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BU18" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="BV18" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="BW18" t="s">
-        <v>131</v>
+        <v>109</v>
       </c>
     </row>
     <row r="19" spans="1:75">
@@ -4970,7 +4901,7 @@
         <v>108</v>
       </c>
       <c r="AD19" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AE19" t="s">
         <v>108</v>
@@ -4994,13 +4925,13 @@
         <v>108</v>
       </c>
       <c r="AL19" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AM19" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AN19" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AO19" t="s">
         <v>108</v>
@@ -5087,25 +5018,25 @@
         <v>108</v>
       </c>
       <c r="BQ19" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BR19" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BS19" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BT19" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BU19" t="s">
-        <v>120</v>
+        <v>109</v>
       </c>
       <c r="BV19" t="s">
-        <v>120</v>
+        <v>109</v>
       </c>
       <c r="BW19" t="s">
-        <v>126</v>
+        <v>109</v>
       </c>
     </row>
     <row r="20" spans="1:75">
@@ -5182,58 +5113,58 @@
         <v>108</v>
       </c>
       <c r="Y20" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="Z20" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AA20" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AB20" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AC20" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AD20" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AE20" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AF20" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AG20" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AH20" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AI20" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AJ20" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AK20" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AL20" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AM20" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AN20" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AO20" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AP20" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AQ20" t="s">
         <v>108</v>
@@ -5314,25 +5245,25 @@
         <v>108</v>
       </c>
       <c r="BQ20" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BR20" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BS20" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BT20" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BU20" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="BV20" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="BW20" t="s">
-        <v>131</v>
+        <v>109</v>
       </c>
     </row>
     <row r="21" spans="1:75">
@@ -5412,58 +5343,58 @@
         <v>108</v>
       </c>
       <c r="Z21" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AA21" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AB21" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AC21" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AD21" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AE21" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AF21" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AG21" t="s">
         <v>108</v>
       </c>
       <c r="AH21" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AI21" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AJ21" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AK21" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AL21" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AM21" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AN21" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AO21" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AP21" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AQ21" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AR21" t="s">
         <v>108</v>
@@ -5541,25 +5472,25 @@
         <v>108</v>
       </c>
       <c r="BQ21" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BR21" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BS21" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BT21" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BU21" t="s">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="BV21" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="BW21" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
     </row>
     <row r="22" spans="1:75">
@@ -5639,52 +5570,52 @@
         <v>108</v>
       </c>
       <c r="Z22" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AA22" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AB22" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AC22" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AD22" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AE22" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AF22" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AG22" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AH22" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AI22" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AJ22" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AK22" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AL22" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AM22" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AN22" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AO22" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AP22" t="s">
         <v>108</v>
@@ -5771,22 +5702,22 @@
         <v>108</v>
       </c>
       <c r="BR22" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BS22" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BT22" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BU22" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="BV22" t="s">
-        <v>120</v>
+        <v>109</v>
       </c>
       <c r="BW22" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
     </row>
     <row r="23" spans="1:75">
@@ -5869,58 +5800,58 @@
         <v>108</v>
       </c>
       <c r="AA23" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AB23" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AC23" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AD23" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AE23" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AF23" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AG23" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AH23" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AI23" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AJ23" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AK23" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AL23" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AM23" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AN23" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AO23" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AP23" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AQ23" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AR23" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AS23" t="s">
         <v>108</v>
@@ -5995,25 +5926,25 @@
         <v>108</v>
       </c>
       <c r="BQ23" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BR23" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BS23" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BT23" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BU23" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="BV23" t="s">
-        <v>120</v>
+        <v>109</v>
       </c>
       <c r="BW23" t="s">
-        <v>131</v>
+        <v>109</v>
       </c>
     </row>
     <row r="24" spans="1:75">
@@ -6093,22 +6024,22 @@
         <v>108</v>
       </c>
       <c r="Z24" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AA24" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AB24" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AC24" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AD24" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AE24" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AF24" t="s">
         <v>108</v>
@@ -6117,34 +6048,34 @@
         <v>108</v>
       </c>
       <c r="AH24" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AI24" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AJ24" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AK24" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AL24" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AM24" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AN24" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AO24" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AP24" t="s">
         <v>108</v>
       </c>
       <c r="AQ24" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AR24" t="s">
         <v>108</v>
@@ -6222,25 +6153,25 @@
         <v>108</v>
       </c>
       <c r="BQ24" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BR24" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BS24" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BT24" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BU24" t="s">
-        <v>122</v>
+        <v>109</v>
       </c>
       <c r="BV24" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="BW24" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
     </row>
     <row r="25" spans="1:75">
@@ -6320,58 +6251,58 @@
         <v>108</v>
       </c>
       <c r="Z25" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AA25" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AB25" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AC25" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AD25" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AE25" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AF25" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AG25" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AH25" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AI25" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AJ25" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AK25" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AL25" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AM25" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AN25" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AO25" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AP25" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AQ25" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AR25" t="s">
         <v>108</v>
@@ -6434,7 +6365,7 @@
         <v>108</v>
       </c>
       <c r="BL25" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BM25" t="s">
         <v>108</v>
@@ -6446,28 +6377,28 @@
         <v>108</v>
       </c>
       <c r="BP25" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BQ25" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BR25" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BS25" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BT25" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BU25" t="s">
-        <v>123</v>
+        <v>109</v>
       </c>
       <c r="BV25" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="BW25" t="s">
-        <v>132</v>
+        <v>109</v>
       </c>
     </row>
     <row r="26" spans="1:75">
@@ -6556,7 +6487,7 @@
         <v>108</v>
       </c>
       <c r="AC26" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AD26" t="s">
         <v>108</v>
@@ -6568,40 +6499,40 @@
         <v>108</v>
       </c>
       <c r="AG26" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AH26" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AI26" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AJ26" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AK26" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AL26" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AM26" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AN26" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AO26" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AP26" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AQ26" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AR26" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AS26" t="s">
         <v>108</v>
@@ -6679,22 +6610,22 @@
         <v>108</v>
       </c>
       <c r="BR26" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BS26" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BT26" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BU26" t="s">
-        <v>124</v>
+        <v>109</v>
       </c>
       <c r="BV26" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="BW26" t="s">
-        <v>125</v>
+        <v>109</v>
       </c>
     </row>
     <row r="27" spans="1:75">
@@ -6771,58 +6702,58 @@
         <v>108</v>
       </c>
       <c r="Y27" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="Z27" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AA27" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AB27" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AC27" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AD27" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AE27" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AF27" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AG27" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AH27" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AI27" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AJ27" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AK27" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AL27" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AM27" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AN27" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AO27" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AP27" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AQ27" t="s">
         <v>108</v>
@@ -6900,28 +6831,28 @@
         <v>108</v>
       </c>
       <c r="BP27" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BQ27" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BR27" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BS27" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BT27" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BU27" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="BV27" t="s">
-        <v>124</v>
+        <v>109</v>
       </c>
       <c r="BW27" t="s">
-        <v>123</v>
+        <v>109</v>
       </c>
     </row>
     <row r="28" spans="1:75">
@@ -7001,61 +6932,61 @@
         <v>108</v>
       </c>
       <c r="Z28" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AA28" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AB28" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AC28" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AD28" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AE28" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AF28" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AG28" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AH28" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AI28" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AJ28" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AK28" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AL28" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AM28" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AN28" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AO28" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AP28" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AQ28" t="s">
         <v>108</v>
       </c>
       <c r="AR28" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AS28" t="s">
         <v>108</v>
@@ -7136,19 +7067,19 @@
         <v>108</v>
       </c>
       <c r="BS28" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BT28" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BU28" t="s">
-        <v>125</v>
+        <v>109</v>
       </c>
       <c r="BV28" t="s">
-        <v>120</v>
+        <v>109</v>
       </c>
       <c r="BW28" t="s">
-        <v>119</v>
+        <v>109</v>
       </c>
     </row>
     <row r="29" spans="1:75">
@@ -7222,64 +7153,64 @@
         <v>108</v>
       </c>
       <c r="X29" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="Y29" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="Z29" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AA29" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AB29" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AC29" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AD29" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AE29" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AF29" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AG29" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AH29" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AI29" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AJ29" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AK29" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AL29" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AM29" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AN29" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AO29" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AP29" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AQ29" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AR29" t="s">
         <v>108</v>
@@ -7357,25 +7288,25 @@
         <v>108</v>
       </c>
       <c r="BQ29" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BR29" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BS29" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BT29" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BU29" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="BV29" t="s">
-        <v>127</v>
+        <v>109</v>
       </c>
       <c r="BW29" t="s">
-        <v>132</v>
+        <v>109</v>
       </c>
     </row>
     <row r="30" spans="1:75">
@@ -7455,55 +7386,55 @@
         <v>108</v>
       </c>
       <c r="Z30" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AA30" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AB30" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AC30" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AD30" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AE30" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AF30" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AG30" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AH30" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AI30" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AJ30" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AK30" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AL30" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AM30" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AN30" t="s">
         <v>108</v>
       </c>
       <c r="AO30" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AP30" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AQ30" t="s">
         <v>108</v>
@@ -7581,28 +7512,28 @@
         <v>108</v>
       </c>
       <c r="BP30" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BQ30" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BR30" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BS30" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BT30" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BU30" t="s">
-        <v>125</v>
+        <v>109</v>
       </c>
       <c r="BV30" t="s">
-        <v>127</v>
+        <v>109</v>
       </c>
       <c r="BW30" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
     </row>
     <row r="31" spans="1:75">
@@ -7682,55 +7613,55 @@
         <v>108</v>
       </c>
       <c r="Z31" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AA31" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AB31" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AC31" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AD31" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AE31" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AF31" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AG31" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AH31" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AI31" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AJ31" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AK31" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AL31" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AM31" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AN31" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AO31" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AP31" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AQ31" t="s">
         <v>108</v>
@@ -7811,25 +7742,25 @@
         <v>108</v>
       </c>
       <c r="BQ31" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BR31" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BS31" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BT31" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BU31" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="BV31" t="s">
-        <v>124</v>
+        <v>109</v>
       </c>
       <c r="BW31" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
     </row>
     <row r="32" spans="1:75">
@@ -7900,61 +7831,61 @@
         <v>108</v>
       </c>
       <c r="W32" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="X32" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="Y32" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="Z32" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AA32" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AB32" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AC32" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AD32" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AE32" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AF32" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AG32" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AH32" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AI32" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AJ32" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AK32" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AL32" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AM32" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AN32" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AO32" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AP32" t="s">
         <v>108</v>
@@ -8035,28 +7966,28 @@
         <v>108</v>
       </c>
       <c r="BP32" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BQ32" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BR32" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BS32" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BT32" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BU32" t="s">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="BV32" t="s">
-        <v>120</v>
+        <v>109</v>
       </c>
       <c r="BW32" t="s">
-        <v>132</v>
+        <v>109</v>
       </c>
     </row>
     <row r="33" spans="1:75">
@@ -8136,58 +8067,58 @@
         <v>108</v>
       </c>
       <c r="Z33" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AA33" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AB33" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AC33" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AD33" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AE33" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AF33" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AG33" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AH33" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AI33" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AJ33" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AK33" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AL33" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AM33" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AN33" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AO33" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AP33" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AQ33" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AR33" t="s">
         <v>108</v>
@@ -8262,28 +8193,28 @@
         <v>108</v>
       </c>
       <c r="BP33" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BQ33" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BR33" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BS33" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BT33" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BU33" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="BV33" t="s">
-        <v>127</v>
+        <v>109</v>
       </c>
       <c r="BW33" t="s">
-        <v>123</v>
+        <v>109</v>
       </c>
     </row>
     <row r="34" spans="1:75">
@@ -8363,58 +8294,58 @@
         <v>108</v>
       </c>
       <c r="Z34" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AA34" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AB34" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AC34" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AD34" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AE34" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AF34" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AG34" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AH34" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AI34" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AJ34" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AK34" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AL34" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AM34" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AN34" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AO34" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AP34" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AQ34" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AR34" t="s">
         <v>108</v>
@@ -8489,28 +8420,28 @@
         <v>108</v>
       </c>
       <c r="BP34" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BQ34" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BR34" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BS34" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BT34" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BU34" t="s">
-        <v>125</v>
+        <v>109</v>
       </c>
       <c r="BV34" t="s">
-        <v>122</v>
+        <v>109</v>
       </c>
       <c r="BW34" t="s">
-        <v>123</v>
+        <v>109</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/Rice_(high_quality)_percentile_classification_matrix.xlsx
+++ b/outputs/Rice_(high_quality)_percentile_classification_matrix.xlsx
@@ -340,7 +340,7 @@
     <t>Zabul</t>
   </si>
   <si>
-    <t>Minimal</t>
+    <t>No concern</t>
   </si>
   <si>
     <t>0%</t>
